--- a/generated/sources/reports/digital/Digital_Weekly_Channel_Report_W42_2026.xlsx
+++ b/generated/sources/reports/digital/Digital_Weekly_Channel_Report_W42_2026.xlsx
@@ -138,19 +138,19 @@
     <t>Pending</t>
   </si>
   <si>
-    <t>ILVARO</t>
+    <t>IRIDIA</t>
   </si>
   <si>
     <t>powder pink</t>
   </si>
   <si>
-    <t>MAIRE</t>
+    <t>AUREA</t>
   </si>
   <si>
     <t>black</t>
   </si>
   <si>
-    <t>AMBRINE</t>
+    <t>AMALIA</t>
   </si>
   <si>
     <t>chocolate</t>
@@ -168,10 +168,10 @@
     <t>J10911A00213-742</t>
   </si>
   <si>
-    <t>ILVARO powder pink: notify-me requests exploded from 02/10 (celebrity photos), KR and CN sites first, then US/GB/FR.</t>
-  </si>
-  <si>
-    <t>MAIRE black: steady requests since late September, mostly from KR and GB sites; back in stock online from 17/10.</t>
+    <t>IRIDIA powder pink: notify-me requests exploded from 02/10 (celebrity photos), KR and CN sites first, then US/GB/FR.</t>
+  </si>
+  <si>
+    <t>AUREA black: steady requests since late September, mostly from KR and GB sites; back in stock online from 17/10.</t>
   </si>
   <si>
     <t>Demand is gross ordered value; Finance reports online net sales after returns and ex VAT - expect ~25-30% difference.</t>
